--- a/xls/square_un_16_tri3_15_0.xlsx
+++ b/xls/square_un_16_tri3_15_0.xlsx
@@ -461,34 +461,34 @@
         <v>11</v>
       </c>
       <c r="B16">
-        <v>297</v>
+        <v>256</v>
       </c>
       <c r="C16" t="s">
         <v>11</v>
       </c>
       <c r="D16">
-        <v>340</v>
+        <v>297</v>
       </c>
       <c r="E16" t="s">
         <v>12</v>
       </c>
       <c r="F16">
-        <v>340</v>
+        <v>297</v>
       </c>
       <c r="G16" t="s">
         <v>13</v>
       </c>
       <c r="H16">
-        <v>1842</v>
+        <v>1596</v>
       </c>
       <c r="I16">
-        <v>-2.010697279608687</v>
+        <v>-2.162049474427453</v>
       </c>
       <c r="J16">
-        <v>-1.67987149013588</v>
+        <v>-1.814097769601885</v>
       </c>
       <c r="K16">
-        <v>-0.3120920588652756</v>
+        <v>-0.5074322988697877</v>
       </c>
     </row>
   </sheetData>

--- a/xls/square_un_16_tri3_15_0.xlsx
+++ b/xls/square_un_16_tri3_15_0.xlsx
@@ -482,13 +482,13 @@
         <v>1596</v>
       </c>
       <c r="I16">
-        <v>-2.162049474427453</v>
+        <v>-2.162968109954059</v>
       </c>
       <c r="J16">
-        <v>-1.814097769601885</v>
+        <v>-1.8143656075809602</v>
       </c>
       <c r="K16">
-        <v>-0.5074322988697877</v>
+        <v>-0.5078282389285799</v>
       </c>
     </row>
   </sheetData>
